--- a/03_ai-threat-modeling-mitre-atlas/exercises/solution/threat_model.xlsx
+++ b/03_ai-threat-modeling-mitre-atlas/exercises/solution/threat_model.xlsx
@@ -729,7 +729,7 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Lead the threat-modeling session for FinTrust IDV ahead of launch. Two ATLAS TTPs are scoped end-to-end as worked examples; you select and scope 3 more from the ATLAS TTP Reference sheet, then produce a 1-page board-facing summary in threat_model_summary_starter.md.</t>
+          <t>Lead the threat-modeling session for FinTrust IDV ahead of launch. Two ATLAS TTPs are scoped end-to-end as worked examples; you scope 3 more (their IDs are pre-selected on the Threat Model sheet; the ATLAS TTP Reference sheet has the full candidate list), then produce a 1-page board-facing summary on the Board Brief sheet.</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="B2" s="24" t="inlineStr">
         <is>
-          <t>ATLAS structures External Harms (AML.T0048) into sub-techniques. The financial-loss case is captured precisely by AML.T0048.001 "Financial Harm" — ATLAS uses the term "Financial Harm" in the catalog.</t>
+          <t>ATLAS structures External Harms (AML.T0048) into sub-techniques. The financial-loss case is captured precisely by AML.T0048.000 "Financial Harm" — ATLAS uses the term "Financial Harm" in the catalog.</t>
         </is>
       </c>
     </row>

--- a/03_ai-threat-modeling-mitre-atlas/exercises/solution/threat_model.xlsx
+++ b/03_ai-threat-modeling-mitre-atlas/exercises/solution/threat_model.xlsx
@@ -931,12 +931,12 @@
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>ML Model Inference API Access</t>
+          <t>AI Model Inference API Access</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>ML Model Access</t>
+          <t>AI Model Access</t>
         </is>
       </c>
       <c r="D3" s="17" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Evade ML Model — Deepfake / Generative-Liveness Bypass</t>
+          <t>Evade AI Model — Deepfake / Generative-Liveness Bypass</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B5" s="12" t="inlineStr">
         <is>
-          <t>Exfiltration via ML Inference API</t>
+          <t>Exfiltration via AI Inference API</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -1214,6 +1214,7 @@
       <c r="D2" s="18" t="n"/>
       <c r="E2" s="19" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="20" t="inlineStr">
         <is>
@@ -1263,7 +1264,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>Evade ML Model — Deepfake / Generative-Liveness Bypass</t>
+          <t>Evade AI Model — Deepfake / Generative-Liveness Bypass</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
@@ -1286,7 +1287,7 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>Exfiltration via ML Inference API (model extraction)</t>
+          <t>Exfiltration via AI Inference API (model extraction)</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
@@ -1321,6 +1322,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="20" t="inlineStr">
         <is>
@@ -1350,7 +1352,7 @@
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>AML.T0015 — Evade ML Model — Deepfake / Generative-Liveness Bypass</t>
+          <t>AML.T0015 — Evade AI Model — Deepfake / Generative-Liveness Bypass</t>
         </is>
       </c>
       <c r="B12" s="19" t="n"/>
@@ -1366,7 +1368,7 @@
     <row r="13" ht="96" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
         <is>
-          <t>AML.T0024 — Exfiltration via ML Inference API (model extraction)</t>
+          <t>AML.T0024 — Exfiltration via AI Inference API (model extraction)</t>
         </is>
       </c>
       <c r="B13" s="19" t="n"/>
@@ -1395,6 +1397,7 @@
       <c r="D14" s="18" t="n"/>
       <c r="E14" s="19" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
@@ -1435,6 +1438,7 @@
       <c r="D18" s="18" t="n"/>
       <c r="E18" s="19" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="13" t="inlineStr">
         <is>
@@ -1574,6 +1578,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="20" t="inlineStr">
         <is>
@@ -1642,6 +1647,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="20" t="inlineStr">
         <is>
@@ -1797,7 +1803,7 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>Evade ML Model</t>
+          <t>Evade AI Model</t>
         </is>
       </c>
       <c r="C4" s="16" t="inlineStr">
@@ -1819,7 +1825,7 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>Backdoor ML Model</t>
+          <t>Backdoor AI Model</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
@@ -1863,7 +1869,7 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>Exfiltration via ML Inference API</t>
+          <t>Exfiltration via AI Inference API</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -1885,7 +1891,7 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>Denial of ML Service</t>
+          <t>Denial of AI Service</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
@@ -1907,12 +1913,12 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>ML Model Inference API Access</t>
+          <t>AI Model Inference API Access</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>ML Model Access</t>
+          <t>AI Model Access</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
@@ -1951,12 +1957,12 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>Full ML Model Access</t>
+          <t>Full AI Model Access</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>ML Model Access</t>
+          <t>AI Model Access</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
@@ -2207,7 +2213,7 @@
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>ATLAS lists Backdoor ML Model under both "Persistence" and "ML Attack Staging" tactics, depending on whether the backdoor is staged before deployment or seeded post-deployment.</t>
+          <t>ATLAS lists Backdoor AI Model under both "Persistence" and "ML Attack Staging" tactics, depending on whether the backdoor is staged before deployment or seeded post-deployment.</t>
         </is>
       </c>
     </row>

--- a/03_ai-threat-modeling-mitre-atlas/exercises/solution/threat_model.xlsx
+++ b/03_ai-threat-modeling-mitre-atlas/exercises/solution/threat_model.xlsx
@@ -1940,7 +1940,7 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>ML Attack Staging</t>
+          <t>AI Attack Staging</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>ATLAS lists Backdoor AI Model under both "Persistence" and "ML Attack Staging" tactics, depending on whether the backdoor is staged before deployment or seeded post-deployment.</t>
+          <t>ATLAS lists Backdoor AI Model under both "Persistence" and "AI Attack Staging" tactics, depending on whether the backdoor is staged before deployment or seeded post-deployment.</t>
         </is>
       </c>
     </row>
